--- a/app/www/profiles/profile-Wine-zgpr-400.xlsx
+++ b/app/www/profiles/profile-Wine-zgpr-400.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workdir\Metabolomic\NMRProcFlow\git\RnmrQuant1D\RnmrQuant1D_UI\www\profiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workdir\Metabolomic\WAP-NMR\Manips\JC-DUB-400\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C49507-4E9A-4755-9CC5-BB19F4947D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC16674-BA86-4834-9F96-13747F105EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2130" yWindow="2445" windowWidth="21600" windowHeight="11235" xr2:uid="{524AC9D9-352A-4B49-9285-9FC9260D37F8}"/>
+    <workbookView xWindow="2595" yWindow="450" windowWidth="25575" windowHeight="14265" xr2:uid="{524AC9D9-352A-4B49-9285-9FC9260D37F8}"/>
   </bookViews>
   <sheets>
     <sheet name="profile-zgpr-400" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -232,9 +232,6 @@
     <t>3.31,3.326,3.316,s</t>
   </si>
   <si>
-    <t>0,1.2,0.55</t>
-  </si>
-  <si>
     <t>choline</t>
   </si>
   <si>
@@ -242,6 +239,9 @@
   </si>
   <si>
     <t>1,330</t>
+  </si>
+  <si>
+    <t>0,5,0.55</t>
   </si>
 </sst>
 </file>
@@ -1294,7 +1294,7 @@
         <v>2</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>63</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" s="5">
         <v>50</v>
@@ -1605,7 +1605,7 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>54</v>
@@ -1652,7 +1652,7 @@
         <v>9.25</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>69</v>
@@ -1757,7 +1757,7 @@
         <v>3.6080000000000001</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G50" s="4">
         <v>0</v>
@@ -1857,7 +1857,7 @@
         <v>43</v>
       </c>
       <c r="B60" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C60">
         <v>104.1708</v>
